--- a/research/traditional_assets/database/data/lithuania/lithuania_computer_services.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_computer_services.xlsx
@@ -587,20 +587,17 @@
           <t>Computer Services</t>
         </is>
       </c>
-      <c r="E2">
-        <v>0.137</v>
-      </c>
       <c r="K2">
-        <v>5.83</v>
+        <v>2.98</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01207885304659498</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.1130872483221477</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -612,34 +609,37 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.337</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="V2">
-        <v>0.07089947089947091</v>
+        <v>0.08530465949820788</v>
       </c>
       <c r="W2">
-        <v>0.1793846153846154</v>
+        <v>0.07215496368038742</v>
       </c>
       <c r="X2">
-        <v>0.06771563811408883</v>
+        <v>0.1154649788357188</v>
       </c>
       <c r="Y2">
-        <v>0.1116689772705266</v>
+        <v>-0.04331001515533141</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.08406078241189784</v>
+        <v>-0.04505437597099948</v>
       </c>
       <c r="AB2">
-        <v>0.06771563811408883</v>
+        <v>0.1154649788357188</v>
       </c>
       <c r="AC2">
-        <v>-0.1517764205259867</v>
+        <v>-0.1605193548067183</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-2.68</v>
+        <v>-2.38</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -660,19 +660,19 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.07630979498861049</v>
+        <v>-0.0932601880877743</v>
       </c>
       <c r="AK2">
-        <v>-0.06939409632314864</v>
+        <v>-0.06146694214876033</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.183</v>
+        <v>-1.64</v>
       </c>
       <c r="AQ2">
-        <v>14.20765027322405</v>
+        <v>1.060975609756098</v>
       </c>
     </row>
     <row r="3">
@@ -691,20 +691,17 @@
           <t>Computer Services</t>
         </is>
       </c>
-      <c r="E3">
-        <v>0.137</v>
-      </c>
       <c r="K3">
-        <v>5.83</v>
+        <v>2.98</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.337</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01207885304659498</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.1130872483221477</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -716,34 +713,37 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.337</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>0.07089947089947091</v>
+        <v>0.08530465949820788</v>
       </c>
       <c r="W3">
-        <v>0.1793846153846154</v>
+        <v>0.07215496368038742</v>
       </c>
       <c r="X3">
-        <v>0.06771563811408883</v>
+        <v>0.1154649788357188</v>
       </c>
       <c r="Y3">
-        <v>0.1116689772705266</v>
+        <v>-0.04331001515533141</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.08406078241189784</v>
+        <v>-0.04505437597099948</v>
       </c>
       <c r="AB3">
-        <v>0.06771563811408883</v>
+        <v>0.1154649788357188</v>
       </c>
       <c r="AC3">
-        <v>-0.1517764205259867</v>
+        <v>-0.1605193548067183</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -755,7 +755,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2.68</v>
+        <v>-2.38</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -764,19 +764,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.07630979498861049</v>
+        <v>-0.0932601880877743</v>
       </c>
       <c r="AK3">
-        <v>-0.06939409632314864</v>
+        <v>-0.06146694214876033</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.183</v>
+        <v>-1.64</v>
       </c>
       <c r="AQ3">
-        <v>14.20765027322405</v>
+        <v>1.060975609756098</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/lithuania/lithuania_computer_services.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_computer_services.xlsx
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="K2">
-        <v>2.98</v>
+        <v>0.405</v>
       </c>
       <c r="M2">
-        <v>0.337</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.01207885304659498</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.1130872483221477</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -609,37 +609,34 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.337</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>0.628</v>
       </c>
       <c r="V2">
-        <v>0.08530465949820788</v>
+        <v>0.02482213438735178</v>
       </c>
       <c r="W2">
-        <v>0.07215496368038742</v>
+        <v>0.01035805626598466</v>
       </c>
       <c r="X2">
-        <v>0.1154649788357188</v>
+        <v>0.09672605231925588</v>
       </c>
       <c r="Y2">
-        <v>-0.04331001515533141</v>
+        <v>-0.08636799605327122</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.04505437597099948</v>
+        <v>-0.01870949119630533</v>
       </c>
       <c r="AB2">
-        <v>0.1154649788357188</v>
+        <v>0.09672605231925588</v>
       </c>
       <c r="AC2">
-        <v>-0.1605193548067183</v>
+        <v>-0.1154355435155612</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -651,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-2.38</v>
+        <v>-0.628</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -660,19 +657,19 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.0932601880877743</v>
+        <v>-0.02545395590142672</v>
       </c>
       <c r="AK2">
-        <v>-0.06146694214876033</v>
+        <v>-0.01595042161942497</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.64</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="AQ2">
-        <v>1.060975609756098</v>
+        <v>0.8780788177339901</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +680,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UTIB INVL Technology (NSEL:INC1L)</t>
+          <t>INVL Technology UTIB (NSEL:INC1L)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -692,16 +689,16 @@
         </is>
       </c>
       <c r="K3">
-        <v>2.98</v>
+        <v>0.405</v>
       </c>
       <c r="M3">
-        <v>0.337</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.01207885304659498</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.1130872483221477</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -713,37 +710,34 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0.337</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>0.628</v>
       </c>
       <c r="V3">
-        <v>0.08530465949820788</v>
+        <v>0.02482213438735178</v>
       </c>
       <c r="W3">
-        <v>0.07215496368038742</v>
+        <v>0.01035805626598466</v>
       </c>
       <c r="X3">
-        <v>0.1154649788357188</v>
+        <v>0.09672605231925588</v>
       </c>
       <c r="Y3">
-        <v>-0.04331001515533141</v>
+        <v>-0.08636799605327122</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.04505437597099948</v>
+        <v>-0.01870949119630533</v>
       </c>
       <c r="AB3">
-        <v>0.1154649788357188</v>
+        <v>0.09672605231925588</v>
       </c>
       <c r="AC3">
-        <v>-0.1605193548067183</v>
+        <v>-0.1154355435155612</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -755,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2.38</v>
+        <v>-0.628</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -764,19 +758,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0932601880877743</v>
+        <v>-0.02545395590142672</v>
       </c>
       <c r="AK3">
-        <v>-0.06146694214876033</v>
+        <v>-0.01595042161942497</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1.64</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="AQ3">
-        <v>1.060975609756098</v>
+        <v>0.8780788177339901</v>
       </c>
     </row>
   </sheetData>
